--- a/outputs/Sorghum_(local)_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_(local)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="90">
   <si>
     <t>2018 Apr</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Yambio</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Minimal</t>
@@ -886,7 +889,7 @@
         <v>79</v>
       </c>
       <c r="Y2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z2" t="s">
         <v>79</v>
@@ -895,19 +898,19 @@
         <v>79</v>
       </c>
       <c r="AB2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="s">
         <v>79</v>
@@ -922,25 +925,25 @@
         <v>79</v>
       </c>
       <c r="AK2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s">
         <v>79</v>
       </c>
       <c r="AN2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR2" t="s">
         <v>79</v>
@@ -952,13 +955,13 @@
         <v>79</v>
       </c>
       <c r="AU2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:49">
@@ -969,145 +972,145 @@
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s">
         <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s">
         <v>79</v>
       </c>
       <c r="V3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="s">
         <v>79</v>
       </c>
       <c r="Z3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL3" t="s">
         <v>81</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>80</v>
-      </c>
       <c r="AM3" t="s">
         <v>79</v>
       </c>
       <c r="AN3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AO3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AP3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AQ3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR3" t="s">
         <v>79</v>
       </c>
       <c r="AS3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AV3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:49">
@@ -1181,37 +1184,37 @@
         <v>79</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD4" t="s">
         <v>79</v>
       </c>
       <c r="AE4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="s">
         <v>79</v>
       </c>
       <c r="AH4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI4" t="s">
         <v>79</v>
@@ -1220,19 +1223,19 @@
         <v>79</v>
       </c>
       <c r="AK4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="s">
         <v>79</v>
       </c>
       <c r="AO4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP4" t="s">
         <v>79</v>
@@ -1241,7 +1244,7 @@
         <v>79</v>
       </c>
       <c r="AR4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS4" t="s">
         <v>79</v>
@@ -1250,13 +1253,13 @@
         <v>79</v>
       </c>
       <c r="AU4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:49">
@@ -1327,40 +1330,40 @@
         <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD5" t="s">
         <v>79</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="s">
         <v>79</v>
       </c>
       <c r="AG5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="s">
         <v>79</v>
@@ -1399,13 +1402,13 @@
         <v>79</v>
       </c>
       <c r="AU5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:49">
@@ -1536,7 +1539,7 @@
         <v>79</v>
       </c>
       <c r="AQ6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR6" t="s">
         <v>79</v>
@@ -1548,13 +1551,13 @@
         <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:49">
@@ -1628,7 +1631,7 @@
         <v>79</v>
       </c>
       <c r="X7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7" t="s">
         <v>79</v>
@@ -1646,7 +1649,7 @@
         <v>79</v>
       </c>
       <c r="AD7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="s">
         <v>79</v>
@@ -1661,7 +1664,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s">
         <v>79</v>
@@ -1682,7 +1685,7 @@
         <v>79</v>
       </c>
       <c r="AP7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ7" t="s">
         <v>79</v>
@@ -1697,13 +1700,13 @@
         <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:49">
@@ -1714,16 +1717,16 @@
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
         <v>79</v>
@@ -1732,7 +1735,7 @@
         <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
         <v>79</v>
@@ -1747,22 +1750,22 @@
         <v>79</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" t="s">
         <v>79</v>
       </c>
       <c r="P8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="s">
         <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T8" t="s">
         <v>79</v>
@@ -1846,13 +1849,13 @@
         <v>79</v>
       </c>
       <c r="AU8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:49">
@@ -1863,10 +1866,10 @@
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>79</v>
@@ -1878,22 +1881,22 @@
         <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s">
         <v>79</v>
       </c>
       <c r="L9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
         <v>79</v>
@@ -1902,106 +1905,106 @@
         <v>79</v>
       </c>
       <c r="P9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s">
         <v>79</v>
       </c>
       <c r="AK9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="s">
         <v>79</v>
       </c>
       <c r="AM9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR9" t="s">
         <v>79</v>
       </c>
       <c r="AS9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AU9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AV9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:49">
@@ -2114,19 +2117,19 @@
         <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP10" t="s">
         <v>79</v>
@@ -2144,13 +2147,13 @@
         <v>79</v>
       </c>
       <c r="AU10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:49">
@@ -2272,13 +2275,13 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="s">
         <v>79</v>
       </c>
       <c r="AP11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ11" t="s">
         <v>79</v>
@@ -2293,13 +2296,13 @@
         <v>79</v>
       </c>
       <c r="AU11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:49">
@@ -2373,10 +2376,10 @@
         <v>79</v>
       </c>
       <c r="X12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z12" t="s">
         <v>79</v>
@@ -2385,7 +2388,7 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s">
         <v>79</v>
@@ -2403,7 +2406,7 @@
         <v>79</v>
       </c>
       <c r="AH12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s">
         <v>79</v>
@@ -2412,10 +2415,10 @@
         <v>79</v>
       </c>
       <c r="AK12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="s">
         <v>79</v>
@@ -2436,19 +2439,19 @@
         <v>79</v>
       </c>
       <c r="AS12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT12" t="s">
         <v>79</v>
       </c>
       <c r="AU12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:49">
@@ -2519,10 +2522,10 @@
         <v>79</v>
       </c>
       <c r="W13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s">
         <v>79</v>
@@ -2531,7 +2534,7 @@
         <v>79</v>
       </c>
       <c r="AA13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="s">
         <v>79</v>
@@ -2555,49 +2558,49 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="s">
         <v>79</v>
       </c>
       <c r="AP13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT13" t="s">
         <v>79</v>
       </c>
       <c r="AU13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:49">
@@ -2626,7 +2629,7 @@
         <v>79</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s">
         <v>79</v>
@@ -2641,49 +2644,49 @@
         <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="s">
         <v>79</v>
       </c>
       <c r="R14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s">
         <v>79</v>
       </c>
       <c r="T14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
       </c>
       <c r="W14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X14" t="s">
         <v>79</v>
       </c>
       <c r="Y14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC14" t="s">
         <v>79</v>
@@ -2695,43 +2698,43 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="s">
         <v>79</v>
       </c>
       <c r="AP14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS14" t="s">
         <v>79</v>
@@ -2740,13 +2743,13 @@
         <v>79</v>
       </c>
       <c r="AU14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:49">
@@ -2757,10 +2760,10 @@
         <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
         <v>79</v>
@@ -2769,133 +2772,133 @@
         <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s">
         <v>79</v>
       </c>
       <c r="M15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O15" t="s">
         <v>79</v>
       </c>
       <c r="P15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R15" t="s">
         <v>79</v>
       </c>
       <c r="S15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s">
         <v>79</v>
       </c>
       <c r="U15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W15" t="s">
         <v>79</v>
       </c>
       <c r="X15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM15" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP15" t="s">
         <v>81</v>
       </c>
-      <c r="AN15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO15" t="s">
+      <c r="AQ15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS15" t="s">
         <v>81</v>
       </c>
-      <c r="AP15" t="s">
-        <v>80</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>80</v>
-      </c>
       <c r="AT15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AV15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AW15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -2963,19 +2966,19 @@
         <v>79</v>
       </c>
       <c r="V16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s">
         <v>79</v>
       </c>
       <c r="Z16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s">
         <v>79</v>
@@ -2990,40 +2993,40 @@
         <v>79</v>
       </c>
       <c r="AE16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s">
         <v>79</v>
       </c>
       <c r="AJ16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="s">
         <v>79</v>
       </c>
       <c r="AN16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ16" t="s">
         <v>79</v>
@@ -3038,13 +3041,13 @@
         <v>79</v>
       </c>
       <c r="AU16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:49">
@@ -3112,19 +3115,19 @@
         <v>79</v>
       </c>
       <c r="V17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W17" t="s">
         <v>79</v>
       </c>
       <c r="X17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA17" t="s">
         <v>79</v>
@@ -3133,19 +3136,19 @@
         <v>79</v>
       </c>
       <c r="AC17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE17" t="s">
         <v>79</v>
       </c>
       <c r="AF17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s">
         <v>79</v>
@@ -3157,28 +3160,28 @@
         <v>79</v>
       </c>
       <c r="AK17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM17" t="s">
         <v>79</v>
       </c>
       <c r="AN17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="s">
         <v>79</v>
       </c>
       <c r="AQ17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS17" t="s">
         <v>79</v>
@@ -3187,13 +3190,13 @@
         <v>79</v>
       </c>
       <c r="AU17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:49">
@@ -3261,25 +3264,25 @@
         <v>79</v>
       </c>
       <c r="V18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC18" t="s">
         <v>79</v>
@@ -3288,46 +3291,46 @@
         <v>79</v>
       </c>
       <c r="AE18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG18" t="s">
         <v>79</v>
       </c>
       <c r="AH18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s">
         <v>79</v>
       </c>
       <c r="AK18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS18" t="s">
         <v>79</v>
@@ -3336,13 +3339,13 @@
         <v>79</v>
       </c>
       <c r="AU18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:49">
@@ -3428,10 +3431,10 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD19" t="s">
         <v>79</v>
@@ -3485,13 +3488,13 @@
         <v>79</v>
       </c>
       <c r="AU19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:49">
@@ -3502,31 +3505,31 @@
         <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s">
         <v>79</v>
       </c>
       <c r="J20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
         <v>79</v>
@@ -3544,88 +3547,88 @@
         <v>79</v>
       </c>
       <c r="Q20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S20" t="s">
         <v>79</v>
       </c>
       <c r="T20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W20" t="s">
         <v>79</v>
       </c>
       <c r="X20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ20" t="s">
         <v>79</v>
       </c>
       <c r="AK20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS20" t="s">
         <v>79</v>
@@ -3634,13 +3637,13 @@
         <v>79</v>
       </c>
       <c r="AU20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AV20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:49">
@@ -3735,7 +3738,7 @@
         <v>79</v>
       </c>
       <c r="AE21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="s">
         <v>79</v>
@@ -3783,13 +3786,13 @@
         <v>79</v>
       </c>
       <c r="AU21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:49">
@@ -3860,34 +3863,34 @@
         <v>79</v>
       </c>
       <c r="W22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X22" t="s">
         <v>79</v>
       </c>
       <c r="Y22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG22" t="s">
         <v>79</v>
@@ -3896,31 +3899,31 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s">
         <v>79</v>
       </c>
       <c r="AK22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s">
         <v>79</v>
       </c>
       <c r="AN22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="s">
         <v>79</v>
       </c>
       <c r="AP22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR22" t="s">
         <v>79</v>
@@ -3932,13 +3935,13 @@
         <v>79</v>
       </c>
       <c r="AU22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:49">
@@ -3976,7 +3979,7 @@
         <v>79</v>
       </c>
       <c r="L23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M23" t="s">
         <v>79</v>
@@ -4009,7 +4012,7 @@
         <v>79</v>
       </c>
       <c r="W23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X23" t="s">
         <v>79</v>
@@ -4036,7 +4039,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG23" t="s">
         <v>79</v>
@@ -4054,7 +4057,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s">
         <v>79</v>
@@ -4072,22 +4075,22 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT23" t="s">
         <v>79</v>
       </c>
       <c r="AU23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:49">
@@ -4104,19 +4107,19 @@
         <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
         <v>79</v>
       </c>
       <c r="I24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J24" t="s">
         <v>79</v>
@@ -4143,10 +4146,10 @@
         <v>79</v>
       </c>
       <c r="R24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T24" t="s">
         <v>79</v>
@@ -4158,22 +4161,22 @@
         <v>79</v>
       </c>
       <c r="W24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="s">
         <v>79</v>
       </c>
       <c r="Z24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s">
         <v>79</v>
@@ -4182,61 +4185,61 @@
         <v>79</v>
       </c>
       <c r="AE24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s">
         <v>79</v>
       </c>
       <c r="AL24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AQ24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AT24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU24" t="s">
+        <v>86</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW24" t="s">
         <v>85</v>
-      </c>
-      <c r="AV24" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:49">
@@ -4367,7 +4370,7 @@
         <v>79</v>
       </c>
       <c r="AQ25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR25" t="s">
         <v>79</v>
@@ -4379,13 +4382,13 @@
         <v>79</v>
       </c>
       <c r="AU25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:49">
@@ -4459,25 +4462,25 @@
         <v>79</v>
       </c>
       <c r="X26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s">
         <v>79</v>
       </c>
       <c r="Z26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC26" t="s">
         <v>79</v>
       </c>
       <c r="AD26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE26" t="s">
         <v>79</v>
@@ -4486,16 +4489,16 @@
         <v>79</v>
       </c>
       <c r="AG26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="s">
         <v>79</v>
@@ -4504,22 +4507,22 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP26" t="s">
         <v>79</v>
       </c>
       <c r="AQ26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS26" t="s">
         <v>79</v>
@@ -4528,13 +4531,13 @@
         <v>79</v>
       </c>
       <c r="AU26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:49">
@@ -4545,28 +4548,28 @@
         <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s">
         <v>79</v>
@@ -4578,28 +4581,28 @@
         <v>79</v>
       </c>
       <c r="N27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O27" t="s">
         <v>79</v>
       </c>
       <c r="P27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S27" t="s">
         <v>79</v>
       </c>
       <c r="T27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V27" t="s">
         <v>79</v>
@@ -4641,31 +4644,31 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AO27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AP27" t="s">
         <v>79</v>
       </c>
       <c r="AQ27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR27" t="s">
         <v>79</v>
@@ -4677,13 +4680,13 @@
         <v>79</v>
       </c>
       <c r="AU27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AV27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:49">
@@ -4757,13 +4760,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA28" t="s">
         <v>79</v>
@@ -4772,52 +4775,52 @@
         <v>79</v>
       </c>
       <c r="AC28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s">
         <v>79</v>
       </c>
       <c r="AK28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL28" t="s">
         <v>79</v>
       </c>
       <c r="AM28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS28" t="s">
         <v>79</v>
@@ -4826,13 +4829,13 @@
         <v>79</v>
       </c>
       <c r="AU28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:49">
@@ -4912,10 +4915,10 @@
         <v>79</v>
       </c>
       <c r="Z29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="s">
         <v>79</v>
@@ -4975,13 +4978,13 @@
         <v>79</v>
       </c>
       <c r="AU29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:49">
@@ -4992,67 +4995,67 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
         <v>79</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s">
         <v>79</v>
       </c>
       <c r="K30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N30" t="s">
         <v>79</v>
       </c>
       <c r="O30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P30" t="s">
         <v>79</v>
       </c>
       <c r="Q30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T30" t="s">
         <v>79</v>
       </c>
       <c r="U30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X30" t="s">
         <v>79</v>
@@ -5064,31 +5067,31 @@
         <v>79</v>
       </c>
       <c r="AA30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AD30" t="s">
         <v>79</v>
       </c>
       <c r="AE30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="s">
         <v>79</v>
       </c>
       <c r="AG30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s">
         <v>79</v>
@@ -5112,10 +5115,10 @@
         <v>79</v>
       </c>
       <c r="AQ30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS30" t="s">
         <v>79</v>
@@ -5124,13 +5127,13 @@
         <v>79</v>
       </c>
       <c r="AU30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AV30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:49">
@@ -5138,16 +5141,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
         <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
         <v>79</v>
@@ -5162,10 +5165,10 @@
         <v>79</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L31" t="s">
         <v>79</v>
@@ -5180,106 +5183,106 @@
         <v>79</v>
       </c>
       <c r="P31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q31" t="s">
         <v>79</v>
       </c>
       <c r="R31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T31" t="s">
         <v>79</v>
       </c>
       <c r="U31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD31" t="s">
         <v>79</v>
       </c>
       <c r="AE31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="s">
         <v>81</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>80</v>
-      </c>
       <c r="AN31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AO31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AV31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_(local)_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_(local)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="82">
   <si>
     <t>2018 Apr</t>
   </si>
@@ -259,31 +259,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>16%</t>
   </si>
 </sst>
 </file>
@@ -910,7 +886,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG2" t="s">
         <v>79</v>
@@ -928,7 +904,7 @@
         <v>80</v>
       </c>
       <c r="AL2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM2" t="s">
         <v>79</v>
@@ -955,13 +931,13 @@
         <v>79</v>
       </c>
       <c r="AU2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:49">
@@ -1044,7 +1020,7 @@
         <v>80</v>
       </c>
       <c r="AA3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="s">
         <v>80</v>
@@ -1068,7 +1044,7 @@
         <v>80</v>
       </c>
       <c r="AI3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s">
         <v>80</v>
@@ -1077,19 +1053,19 @@
         <v>80</v>
       </c>
       <c r="AL3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="s">
         <v>79</v>
       </c>
       <c r="AN3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AQ3" t="s">
         <v>80</v>
@@ -1104,13 +1080,13 @@
         <v>80</v>
       </c>
       <c r="AU3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AW3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:49">
@@ -1184,7 +1160,7 @@
         <v>79</v>
       </c>
       <c r="X4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s">
         <v>80</v>
@@ -1196,7 +1172,7 @@
         <v>80</v>
       </c>
       <c r="AB4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s">
         <v>80</v>
@@ -1205,7 +1181,7 @@
         <v>79</v>
       </c>
       <c r="AE4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF4" t="s">
         <v>80</v>
@@ -1214,7 +1190,7 @@
         <v>79</v>
       </c>
       <c r="AH4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s">
         <v>79</v>
@@ -1253,13 +1229,13 @@
         <v>79</v>
       </c>
       <c r="AU4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:49">
@@ -1330,40 +1306,40 @@
         <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD5" t="s">
         <v>79</v>
       </c>
       <c r="AE5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="s">
         <v>79</v>
       </c>
       <c r="AG5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s">
         <v>79</v>
@@ -1402,13 +1378,13 @@
         <v>79</v>
       </c>
       <c r="AU5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:49">
@@ -1539,7 +1515,7 @@
         <v>79</v>
       </c>
       <c r="AQ6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR6" t="s">
         <v>79</v>
@@ -1551,13 +1527,13 @@
         <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:49">
@@ -1631,7 +1607,7 @@
         <v>79</v>
       </c>
       <c r="X7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s">
         <v>79</v>
@@ -1664,7 +1640,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s">
         <v>79</v>
@@ -1700,13 +1676,13 @@
         <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:49">
@@ -1720,13 +1696,13 @@
         <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s">
         <v>79</v>
@@ -1762,7 +1738,7 @@
         <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s">
         <v>80</v>
@@ -1849,13 +1825,13 @@
         <v>79</v>
       </c>
       <c r="AU8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:49">
@@ -1962,7 +1938,7 @@
         <v>80</v>
       </c>
       <c r="AI9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s">
         <v>79</v>
@@ -1995,16 +1971,16 @@
         <v>80</v>
       </c>
       <c r="AT9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AU9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AV9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:49">
@@ -2117,19 +2093,19 @@
         <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AN10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP10" t="s">
         <v>79</v>
@@ -2147,13 +2123,13 @@
         <v>79</v>
       </c>
       <c r="AU10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:49">
@@ -2275,13 +2251,13 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO11" t="s">
         <v>79</v>
       </c>
       <c r="AP11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ11" t="s">
         <v>79</v>
@@ -2296,13 +2272,13 @@
         <v>79</v>
       </c>
       <c r="AU11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:49">
@@ -2376,7 +2352,7 @@
         <v>79</v>
       </c>
       <c r="X12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y12" t="s">
         <v>80</v>
@@ -2388,7 +2364,7 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC12" t="s">
         <v>79</v>
@@ -2406,7 +2382,7 @@
         <v>79</v>
       </c>
       <c r="AH12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s">
         <v>79</v>
@@ -2418,7 +2394,7 @@
         <v>80</v>
       </c>
       <c r="AL12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s">
         <v>79</v>
@@ -2439,19 +2415,19 @@
         <v>79</v>
       </c>
       <c r="AS12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AT12" t="s">
         <v>79</v>
       </c>
       <c r="AU12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:49">
@@ -2564,43 +2540,43 @@
         <v>80</v>
       </c>
       <c r="AK13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s">
         <v>80</v>
       </c>
       <c r="AN13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s">
         <v>79</v>
       </c>
       <c r="AP13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AT13" t="s">
         <v>79</v>
       </c>
       <c r="AU13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:49">
@@ -2707,10 +2683,10 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s">
         <v>80</v>
@@ -2731,7 +2707,7 @@
         <v>80</v>
       </c>
       <c r="AQ14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR14" t="s">
         <v>80</v>
@@ -2743,13 +2719,13 @@
         <v>79</v>
       </c>
       <c r="AU14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AW14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:49">
@@ -2856,28 +2832,28 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s">
         <v>80</v>
       </c>
       <c r="AK15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s">
         <v>80</v>
       </c>
       <c r="AO15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AQ15" t="s">
         <v>80</v>
@@ -2886,19 +2862,19 @@
         <v>79</v>
       </c>
       <c r="AS15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AT15" t="s">
         <v>80</v>
       </c>
       <c r="AU15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AV15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AW15" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -2969,7 +2945,7 @@
         <v>80</v>
       </c>
       <c r="W16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X16" t="s">
         <v>80</v>
@@ -2993,16 +2969,16 @@
         <v>79</v>
       </c>
       <c r="AE16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG16" t="s">
         <v>80</v>
       </c>
       <c r="AH16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s">
         <v>79</v>
@@ -3011,7 +2987,7 @@
         <v>80</v>
       </c>
       <c r="AK16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s">
         <v>80</v>
@@ -3020,13 +2996,13 @@
         <v>79</v>
       </c>
       <c r="AN16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ16" t="s">
         <v>79</v>
@@ -3041,13 +3017,13 @@
         <v>79</v>
       </c>
       <c r="AU16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:49">
@@ -3121,7 +3097,7 @@
         <v>79</v>
       </c>
       <c r="X17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s">
         <v>80</v>
@@ -3139,7 +3115,7 @@
         <v>80</v>
       </c>
       <c r="AD17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE17" t="s">
         <v>79</v>
@@ -3169,7 +3145,7 @@
         <v>79</v>
       </c>
       <c r="AN17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s">
         <v>80</v>
@@ -3178,7 +3154,7 @@
         <v>79</v>
       </c>
       <c r="AQ17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR17" t="s">
         <v>80</v>
@@ -3190,13 +3166,13 @@
         <v>79</v>
       </c>
       <c r="AU17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:49">
@@ -3264,13 +3240,13 @@
         <v>79</v>
       </c>
       <c r="V18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W18" t="s">
         <v>80</v>
       </c>
       <c r="X18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s">
         <v>80</v>
@@ -3300,7 +3276,7 @@
         <v>79</v>
       </c>
       <c r="AH18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s">
         <v>80</v>
@@ -3321,10 +3297,10 @@
         <v>80</v>
       </c>
       <c r="AO18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ18" t="s">
         <v>80</v>
@@ -3339,13 +3315,13 @@
         <v>79</v>
       </c>
       <c r="AU18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:49">
@@ -3431,10 +3407,10 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s">
         <v>79</v>
@@ -3488,13 +3464,13 @@
         <v>79</v>
       </c>
       <c r="AU19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:49">
@@ -3568,7 +3544,7 @@
         <v>79</v>
       </c>
       <c r="X20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y20" t="s">
         <v>80</v>
@@ -3598,10 +3574,10 @@
         <v>80</v>
       </c>
       <c r="AH20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s">
         <v>79</v>
@@ -3637,13 +3613,13 @@
         <v>79</v>
       </c>
       <c r="AU20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AV20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:49">
@@ -3738,7 +3714,7 @@
         <v>79</v>
       </c>
       <c r="AE21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s">
         <v>79</v>
@@ -3786,13 +3762,13 @@
         <v>79</v>
       </c>
       <c r="AU21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:49">
@@ -3875,13 +3851,13 @@
         <v>80</v>
       </c>
       <c r="AA22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB22" t="s">
         <v>80</v>
       </c>
       <c r="AC22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD22" t="s">
         <v>80</v>
@@ -3890,7 +3866,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG22" t="s">
         <v>79</v>
@@ -3935,13 +3911,13 @@
         <v>79</v>
       </c>
       <c r="AU22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:49">
@@ -3979,7 +3955,7 @@
         <v>79</v>
       </c>
       <c r="L23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M23" t="s">
         <v>79</v>
@@ -4012,7 +3988,7 @@
         <v>79</v>
       </c>
       <c r="W23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X23" t="s">
         <v>79</v>
@@ -4057,7 +4033,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s">
         <v>79</v>
@@ -4078,19 +4054,19 @@
         <v>80</v>
       </c>
       <c r="AS23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AT23" t="s">
         <v>79</v>
       </c>
       <c r="AU23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:49">
@@ -4218,7 +4194,7 @@
         <v>80</v>
       </c>
       <c r="AP24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AQ24" t="s">
         <v>80</v>
@@ -4227,19 +4203,19 @@
         <v>80</v>
       </c>
       <c r="AS24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AT24" t="s">
         <v>80</v>
       </c>
       <c r="AU24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AV24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AW24" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:49">
@@ -4370,7 +4346,7 @@
         <v>79</v>
       </c>
       <c r="AQ25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR25" t="s">
         <v>79</v>
@@ -4382,13 +4358,13 @@
         <v>79</v>
       </c>
       <c r="AU25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:49">
@@ -4468,7 +4444,7 @@
         <v>79</v>
       </c>
       <c r="Z26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA26" t="s">
         <v>80</v>
@@ -4480,7 +4456,7 @@
         <v>79</v>
       </c>
       <c r="AD26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE26" t="s">
         <v>79</v>
@@ -4489,13 +4465,13 @@
         <v>79</v>
       </c>
       <c r="AG26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s">
         <v>80</v>
@@ -4513,16 +4489,16 @@
         <v>80</v>
       </c>
       <c r="AO26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP26" t="s">
         <v>79</v>
       </c>
       <c r="AQ26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS26" t="s">
         <v>79</v>
@@ -4531,13 +4507,13 @@
         <v>79</v>
       </c>
       <c r="AU26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:49">
@@ -4563,10 +4539,10 @@
         <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s">
         <v>80</v>
@@ -4647,28 +4623,28 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AK27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="s">
         <v>80</v>
       </c>
       <c r="AN27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AO27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AP27" t="s">
         <v>79</v>
       </c>
       <c r="AQ27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR27" t="s">
         <v>79</v>
@@ -4680,13 +4656,13 @@
         <v>79</v>
       </c>
       <c r="AU27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AV27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:49">
@@ -4760,13 +4736,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y28" t="s">
         <v>80</v>
       </c>
       <c r="Z28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA28" t="s">
         <v>79</v>
@@ -4787,13 +4763,13 @@
         <v>80</v>
       </c>
       <c r="AG28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s">
         <v>79</v>
@@ -4805,10 +4781,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s">
         <v>80</v>
@@ -4829,13 +4805,13 @@
         <v>79</v>
       </c>
       <c r="AU28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:49">
@@ -4915,10 +4891,10 @@
         <v>79</v>
       </c>
       <c r="Z29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB29" t="s">
         <v>79</v>
@@ -4978,13 +4954,13 @@
         <v>79</v>
       </c>
       <c r="AU29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:49">
@@ -4995,7 +4971,7 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
         <v>80</v>
@@ -5022,10 +4998,10 @@
         <v>80</v>
       </c>
       <c r="L30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N30" t="s">
         <v>79</v>
@@ -5067,13 +5043,13 @@
         <v>79</v>
       </c>
       <c r="AA30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB30" t="s">
         <v>80</v>
       </c>
       <c r="AC30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD30" t="s">
         <v>79</v>
@@ -5088,10 +5064,10 @@
         <v>80</v>
       </c>
       <c r="AH30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s">
         <v>79</v>
@@ -5118,7 +5094,7 @@
         <v>80</v>
       </c>
       <c r="AR30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS30" t="s">
         <v>79</v>
@@ -5127,13 +5103,13 @@
         <v>79</v>
       </c>
       <c r="AU30" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AV30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW30" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:49">
@@ -5240,7 +5216,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s">
         <v>80</v>
@@ -5252,10 +5228,10 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AO31" t="s">
         <v>80</v>
@@ -5276,13 +5252,13 @@
         <v>80</v>
       </c>
       <c r="AU31" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AV31" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AW31" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_(local)_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_(local)_tukey_classification_matrix.xlsx
@@ -256,7 +256,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
